--- a/AAII_Financials/Quarterly/ACPS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ACPS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>ACPS</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1547,8 +1547,8 @@
       <c r="G41" s="3">
         <v>0</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
+      <c r="H41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>5</v>
@@ -1605,8 +1605,8 @@
       <c r="G43" s="3">
         <v>0</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
@@ -1692,8 +1692,8 @@
       <c r="G46" s="3">
         <v>0</v>
       </c>
-      <c r="H46" s="3">
-        <v>0</v>
+      <c r="H46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>5</v>
@@ -1750,8 +1750,8 @@
       <c r="G48" s="3">
         <v>0</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
@@ -1779,8 +1779,8 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>5</v>
@@ -1924,8 +1924,8 @@
       <c r="G54" s="3">
         <v>0</v>
       </c>
-      <c r="H54" s="3">
-        <v>0</v>
+      <c r="H54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>5</v>
@@ -1979,8 +1979,8 @@
       <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
-        <v>100</v>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
@@ -2008,8 +2008,8 @@
       <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
-        <v>800</v>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>5</v>
@@ -2037,8 +2037,8 @@
       <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
-        <v>300</v>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
@@ -2066,8 +2066,8 @@
       <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="H60" s="3">
-        <v>1100</v>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>5</v>
@@ -2240,8 +2240,8 @@
       <c r="G66" s="3">
         <v>1200</v>
       </c>
-      <c r="H66" s="3">
-        <v>1100</v>
+      <c r="H66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>5</v>
@@ -2398,8 +2398,8 @@
       <c r="G72" s="3">
         <v>-2600</v>
       </c>
-      <c r="H72" s="3">
-        <v>-2500</v>
+      <c r="H72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
@@ -2514,8 +2514,8 @@
       <c r="G76" s="3">
         <v>-1100</v>
       </c>
-      <c r="H76" s="3">
-        <v>-1100</v>
+      <c r="H76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>5</v>
